--- a/Statistics/100m Butterfly_statistics.xlsx
+++ b/Statistics/100m Butterfly_statistics.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G176"/>
+  <dimension ref="A1:G181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -931,20 +931,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.00,10</t>
+          <t>59,50</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>502</v>
+        <v>515</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>15.11.2024</t>
+          <t>28.11.2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bodø</t>
+          <t>Reykjavík</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1311,25 +1311,25 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sindre Søderlund</t>
+          <t>Balder Baarholm</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.03,78</t>
+          <t>1.03,37</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>04.10.2008</t>
+          <t>26.10.2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1346,20 +1346,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Margaret Kjøraas</t>
+          <t>Sindre Søderlund</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.12,22</t>
+          <t>1.03,78</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>04.02.2005</t>
+          <t>04.10.2008</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1416,25 +1416,25 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Balder Baarholm</t>
+          <t>Margaret Kjøraas</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.03,91</t>
+          <t>1.12,22</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>08.06.2025</t>
+          <t>04.02.2005</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Porsgrunn</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1626,12 +1626,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Christoffer Solberg Jørgensen</t>
+          <t>Sebastian Amundsen</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.04,56</t>
+          <t>1.04,54</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>04.10.2014</t>
+          <t>29.09.2019</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1661,12 +1661,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sebastian Amundsen</t>
+          <t>Vegard Skjervold</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.04,54</t>
+          <t>1.04,53</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>29.09.2019</t>
+          <t>16.11.2019</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1696,12 +1696,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Vegard Skjervold</t>
+          <t>Christoffer Solberg Jørgensen</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.04,53</t>
+          <t>1.04,56</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>16.11.2019</t>
+          <t>04.10.2014</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2011,25 +2011,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Thomas Trøite</t>
+          <t>Mattias Isaksen</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.06,12</t>
+          <t>1.05,76</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>26.10.2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2046,20 +2046,20 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ask Yifei Baldersheim</t>
+          <t>Thomas Trøite</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.06,17</t>
+          <t>1.06,12</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>13.11.2021</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2081,20 +2081,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kjersti Arefjord</t>
+          <t>Ask Yifei Baldersheim</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.15,33</t>
+          <t>1.06,17</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>17.01.2020</t>
+          <t>13.11.2021</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2116,16 +2116,16 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Maxim Sergeevich Gorodkov</t>
+          <t>Kjersti Arefjord</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.06,63</t>
+          <t>1.15,33</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2186,20 +2186,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Erlend Skogland</t>
+          <t>Maxim Sergeevich Gorodkov</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.06,87</t>
+          <t>1.06,63</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>22.01.2011</t>
+          <t>17.01.2020</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2221,20 +2221,20 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Joakim I. Larsen</t>
+          <t>Erlend Skogland</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.07,07</t>
+          <t>1.06,87</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>24.01.2009</t>
+          <t>22.01.2011</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2256,20 +2256,20 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Tor Arne Hegvik</t>
+          <t>Joakim I. Larsen</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.08,08</t>
+          <t>1.07,07</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>16.09.2007</t>
+          <t>24.01.2009</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2326,20 +2326,20 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Simon Perssønn Mørseth</t>
+          <t>Tor Arne Hegvik</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1.08,37</t>
+          <t>1.08,08</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>17.01.2025</t>
+          <t>16.09.2007</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2361,25 +2361,25 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Emmelin Munkhaugen</t>
+          <t>Simon Perssønn Mørseth</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1.18,08</t>
+          <t>1.08,37</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>08.06.2025</t>
+          <t>17.01.2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Porsgrunn</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2396,25 +2396,25 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Thais Farias Kristiansen</t>
+          <t>Bjørn Eimar Endal Sorteberg</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1.18,17</t>
+          <t>1.08,39</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>08.06.2019</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Klepp</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2431,25 +2431,25 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Tomas Aarvak</t>
+          <t>Emmelin Munkhaugen</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1.09,22</t>
+          <t>1.18,08</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>29.03.2014</t>
+          <t>08.06.2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kristiansand</t>
+          <t>Porsgrunn</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2466,25 +2466,25 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Joakim Gjerde</t>
+          <t>Thais Farias Kristiansen</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1.09,40</t>
+          <t>1.18,17</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>05.12.2015</t>
+          <t>08.06.2019</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Klepp</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2501,25 +2501,25 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Vetle Henriksen</t>
+          <t>Tomas Aarvak</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1.09,41</t>
+          <t>1.09,22</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>18.04.2010</t>
+          <t>29.03.2014</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sognsvann</t>
+          <t>Kristiansand</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2536,25 +2536,25 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Andreas Aglen Alsos</t>
+          <t>Joakim Gjerde</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1.09,47</t>
+          <t>1.09,40</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>18.03.2023</t>
+          <t>05.12.2015</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2571,25 +2571,25 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Hasith Ransiri Attanapola</t>
+          <t>Vetle Henriksen</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1.09,43</t>
+          <t>1.09,41</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>01.12.2018</t>
+          <t>18.04.2010</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Sognsvann</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2606,20 +2606,20 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mattias Isaksen</t>
+          <t>Andreas Aglen Alsos</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1.10,00</t>
+          <t>1.09,47</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>17.01.2025</t>
+          <t>18.03.2023</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2641,25 +2641,25 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Hans Ourson Liem</t>
+          <t>Hasith Ransiri Attanapola</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1.10,26</t>
+          <t>1.09,43</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>06.06.2022</t>
+          <t>01.12.2018</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lambertseter</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2676,25 +2676,25 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Einar Woldseth</t>
+          <t>Vishnu Sattanathan</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1.10,29</t>
+          <t>1.09,47</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>16.03.2024</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2711,20 +2711,20 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Stian Nilsen</t>
+          <t>Einar Woldseth</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1.10,48</t>
+          <t>1.09,77</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>22.01.2011</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2746,25 +2746,25 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Tobias Gilbu</t>
+          <t>Hans Ourson Liem</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1.10,74</t>
+          <t>1.10,26</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>16.11.2019</t>
+          <t>06.06.2022</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Lambertseter</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2781,20 +2781,20 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Olav Ferdinand Pedersen</t>
+          <t>Stian Nilsen</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1.10,72</t>
+          <t>1.10,48</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>09.04.2016</t>
+          <t>22.01.2011</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2816,25 +2816,25 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Birk Skaalvik Trelstad</t>
+          <t>Olav Ferdinand Pedersen</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1.10,91</t>
+          <t>1.10,72</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>16.03.2024</t>
+          <t>09.04.2016</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2851,20 +2851,20 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sondre Brunvoll Møllerløkken</t>
+          <t>Tobias Gilbu</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1.11,04</t>
+          <t>1.10,74</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>16.11.2019</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2886,25 +2886,25 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Reidar Lorentzen</t>
+          <t>Birk Skaalvik Trelstad</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1.11,03</t>
+          <t>1.10,91</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>05.04.2008</t>
+          <t>16.03.2024</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Asker</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2921,25 +2921,25 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Olav Nygård Bergum</t>
+          <t>Sondre Brunvoll Møllerløkken</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1.11,18</t>
+          <t>1.10,88</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2956,25 +2956,25 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Erlend Søderlund</t>
+          <t>Reidar Lorentzen</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1.11,23</t>
+          <t>1.11,03</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>07.04.2013</t>
+          <t>05.04.2008</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Fauske</t>
+          <t>Asker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2991,25 +2991,25 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Håkon Johansen</t>
+          <t>Olav Nygård Bergum</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1.11,31</t>
+          <t>1.11,18</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>24.03.2007</t>
+          <t>15.03.2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3026,25 +3026,25 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Elian Theodor Kringstad</t>
+          <t>Lucas Nachappa Muthanna</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1.12,20</t>
+          <t>1.11,09</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>16.03.2024</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3061,25 +3061,25 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Vårin Berge Jensås</t>
+          <t>Erlend Søderlund</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1.21,77</t>
+          <t>1.11,23</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>18.01.2019</t>
+          <t>07.04.2013</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Fauske</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3096,25 +3096,25 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Aksel Viken Refseth</t>
+          <t>Håkon Johansen</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1.12,49</t>
+          <t>1.11,31</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>17.01.2025</t>
+          <t>24.03.2007</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3131,25 +3131,25 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Oliver Grøtte Ramstad</t>
+          <t>Storm Olander Øvergård</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1.13,66</t>
+          <t>1.12,07</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3166,25 +3166,25 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Alfred Fenstad Høysæter</t>
+          <t>Elian Theodor Kringstad</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1.14,00</t>
+          <t>1.12,20</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>04.09.2021</t>
+          <t>16.03.2024</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3201,20 +3201,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sigurd Rodal Leirgulen</t>
+          <t>Vårin Berge Jensås</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1.14,04</t>
+          <t>1.21,77</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>16.11.2019</t>
+          <t>18.01.2019</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3236,25 +3236,25 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Bjørn Eimar Endal Sorteberg</t>
+          <t>Aksel Viken Refseth</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1.14,35</t>
+          <t>1.12,49</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>17.01.2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3271,25 +3271,25 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Theodor Solheim</t>
+          <t>Oliver Grøtte Ramstad</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1.14,40</t>
+          <t>1.13,66</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>04.09.2021</t>
+          <t>15.03.2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3306,25 +3306,25 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Bjørnar Bakkejord</t>
+          <t>Alfred Fenstad Høysæter</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1.14,43</t>
+          <t>1.14,00</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>24.06.2007</t>
+          <t>04.09.2021</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3341,20 +3341,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Carl Victor Mukisa Nygård</t>
+          <t>Sigurd Rodal Leirgulen</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1.14,41</t>
+          <t>1.14,04</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>18.03.2023</t>
+          <t>16.11.2019</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3376,25 +3376,25 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Vishnu Sattanathan</t>
+          <t>Bjørnar Bakkejord</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1.14,54</t>
+          <t>1.14,43</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>01.12.2024</t>
+          <t>24.06.2007</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3411,20 +3411,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Iris Elise Moen</t>
+          <t>Carl Victor Mukisa Nygård</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1.24,75</t>
+          <t>1.14,41</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>18.04.2021</t>
+          <t>18.03.2023</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3446,25 +3446,25 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>David Fjeld</t>
+          <t>Theodor Solheim</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1.15,05</t>
+          <t>1.14,40</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>16.09.2007</t>
+          <t>04.09.2021</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3481,20 +3481,20 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Bjørn Erik Ystenes</t>
+          <t>Iris Elise Moen</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1.15,25</t>
+          <t>1.24,75</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>03.11.2012</t>
+          <t>18.04.2021</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3516,20 +3516,20 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sander Løvås</t>
+          <t>David Fjeld</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1.15,40</t>
+          <t>1.15,05</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>17.01.2025</t>
+          <t>16.09.2007</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3551,20 +3551,20 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Thomas Stur Ekrem</t>
+          <t>Bjørn Erik Ystenes</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1.15,65</t>
+          <t>1.15,25</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>26.01.2024</t>
+          <t>03.11.2012</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3586,16 +3586,16 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Lucas Nachappa Muthanna</t>
+          <t>Sander Løvås</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1.15,66</t>
+          <t>1.15,40</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -3656,20 +3656,20 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Jakob Isaksen</t>
+          <t>Thomas Stur Ekrem</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1.16,88</t>
+          <t>1.15,65</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>18.03.2023</t>
+          <t>26.01.2024</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3691,25 +3691,25 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sondre Grimsmo</t>
+          <t>Lev Shestov</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1.17,41</t>
+          <t>1.15,69</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>09.02.2008</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3726,25 +3726,25 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Dhanushi Attanapola</t>
+          <t>Jakob Isaksen</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1.27,59</t>
+          <t>1.16,88</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>24.05.2009</t>
+          <t>18.03.2023</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3761,25 +3761,25 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Storm Olander Øvergård</t>
+          <t>Sondre Grimsmo</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1.17,69</t>
+          <t>1.17,41</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>09.02.2008</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3796,25 +3796,25 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Erin Elizabeth Bachynski</t>
+          <t>Dhanushi Attanapola</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1.27,99</t>
+          <t>1.27,59</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>09.04.2016</t>
+          <t>24.05.2009</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3831,25 +3831,25 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Ludvig Svendsen</t>
+          <t>Erin Elizabeth Bachynski</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1.18,19</t>
+          <t>1.27,99</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>09.04.2016</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3866,25 +3866,25 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Torbjørn Ekrem</t>
+          <t>Ludvig Svendsen</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1.18,40</t>
+          <t>1.18,19</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>10.05.2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3901,25 +3901,25 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Edvard Hamnes Ulriksen</t>
+          <t>Torbjørn Ekrem</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1.18,57</t>
+          <t>1.18,40</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>08.06.2025</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Porsgrunn</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3936,12 +3936,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Even Kristoffer Lind Bøckman</t>
+          <t>Edvard Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1.18,65</t>
+          <t>1.18,57</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>16.03.2019</t>
+          <t>08.06.2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Porsgrunn</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3971,25 +3971,25 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Lionel Nicolas Weissbrodt</t>
+          <t>Even Kristoffer Lind Bøckman</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1.19,05</t>
+          <t>1.18,65</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>16.03.2024</t>
+          <t>16.03.2019</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4006,12 +4006,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ingjerd Jepsen Vegge</t>
+          <t>Lionel Nicolas Weissbrodt</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1.29,44</t>
+          <t>1.19,05</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -4019,12 +4019,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>29.10.2011</t>
+          <t>16.03.2024</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4041,20 +4041,20 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Henning Andersson</t>
+          <t>Ingjerd Jepsen Vegge</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1.19,32</t>
+          <t>1.29,44</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>12.01.2013</t>
+          <t>29.10.2011</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4076,25 +4076,25 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Pedro Manquehual</t>
+          <t>Henning Andersson</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1.19,58</t>
+          <t>1.19,32</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>12.01.2013</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4111,25 +4111,25 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Edvin Aurstad Bergum</t>
+          <t>Pedro Manquehual</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1.19,80</t>
+          <t>1.19,58</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>10.05.2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4146,25 +4146,25 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>David Csejtey</t>
+          <t>Edvin Aurstad Bergum</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1.20,02</t>
+          <t>1.19,80</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>19.09.2020</t>
+          <t>15.03.2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4181,25 +4181,25 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Vegard S. Wigum</t>
+          <t>Eirik Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1.20,53</t>
+          <t>1.19,92</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>08.02.2014</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4216,20 +4216,20 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Kristin Myhr Pettersen</t>
+          <t>David Csejtey</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1.31,61</t>
+          <t>1.20,02</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>02.11.2013</t>
+          <t>19.09.2020</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4251,25 +4251,25 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Johan Mostervik</t>
+          <t>Vegard S. Wigum</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1.20,97</t>
+          <t>1.20,53</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>10.02.2018</t>
+          <t>08.02.2014</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4286,20 +4286,20 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Leander Gisvold Restad</t>
+          <t>Kristin Myhr Pettersen</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1.21,10</t>
+          <t>1.31,61</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>17.01.2020</t>
+          <t>02.11.2013</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4321,20 +4321,20 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Jonas D. Lesund</t>
+          <t>Johan Mostervik</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1.21,53</t>
+          <t>1.20,97</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>18.01.2014</t>
+          <t>10.02.2018</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4356,20 +4356,20 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Morten Schanke</t>
+          <t>Leander Gisvold Restad</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1.21,80</t>
+          <t>1.21,10</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>09.04.2016</t>
+          <t>17.01.2020</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4391,20 +4391,20 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Jon Noé Høye</t>
+          <t>Jonas D. Lesund</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1.22,16</t>
+          <t>1.21,53</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>16.11.2019</t>
+          <t>18.01.2014</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4426,25 +4426,25 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Edvin Grenne Spangelo</t>
+          <t>Morten Schanke</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1.22,93</t>
+          <t>1.21,80</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>09.04.2016</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4461,25 +4461,25 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Lyder Ringsvold Hogstad</t>
+          <t>Jon Noé Høye</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1.23,01</t>
+          <t>1.22,16</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>16.03.2019</t>
+          <t>16.11.2019</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4496,25 +4496,25 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Paal Aagaard</t>
+          <t>Edvin Grenne Spangelo</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1.23,38</t>
+          <t>1.22,93</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>13.03.2009</t>
+          <t>15.03.2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Kirkenes</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4531,25 +4531,25 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Anton Sergeevich Gorodkov</t>
+          <t>Lyder Ringsvold Hogstad</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1.23,69</t>
+          <t>1.23,01</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>07.02.2015</t>
+          <t>16.03.2019</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4566,25 +4566,25 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Finn Øivind Fevang</t>
+          <t>Paal Aagaard</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1.23,70</t>
+          <t>1.23,38</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>18.09.2005</t>
+          <t>13.03.2009</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kirkenes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4601,25 +4601,25 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Daniel Haugen Ngwenya</t>
+          <t>Anton Sergeevich Gorodkov</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1.23,94</t>
+          <t>1.23,69</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>16.09.2007</t>
+          <t>07.02.2015</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4636,25 +4636,25 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ellen Kristine Eidsmo Hova</t>
+          <t>Finn Øivind Fevang</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1.35,09</t>
+          <t>1.23,70</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>18.09.2005</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4671,20 +4671,20 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Daniel Stanislaw Czuba</t>
+          <t>Lin Carola Magdalene Nygren</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1.24,31</t>
+          <t>1.32,38</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>17.01.2025</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4706,20 +4706,20 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Kristian Myhr Høgstøl</t>
+          <t>Daniel Haugen Ngwenya</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1.24,73</t>
+          <t>1.23,94</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>19.09.2020</t>
+          <t>16.09.2007</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4741,16 +4741,16 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Eirik Hamnes Ulriksen</t>
+          <t>Ellen Kristine Eidsmo Hova</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1.24,88</t>
+          <t>1.35,09</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -4776,20 +4776,20 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Vegard Maaø</t>
+          <t>Daniel Stanislaw Czuba</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1.25,82</t>
+          <t>1.24,31</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>09.10.2010</t>
+          <t>17.01.2025</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4811,20 +4811,20 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Magnus Svindland Næsgaard</t>
+          <t>Kristian Myhr Høgstøl</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1.26,13</t>
+          <t>1.24,73</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>13.11.2021</t>
+          <t>19.09.2020</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4846,20 +4846,20 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Emily Liv Liem</t>
+          <t>Vegard Maaø</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1.38,08</t>
+          <t>1.25,82</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>22.06.2019</t>
+          <t>09.10.2010</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4881,20 +4881,20 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Conrad Sippala Hassel</t>
+          <t>Magnus Svindland Næsgaard</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1.27,23</t>
+          <t>1.26,13</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>17.01.2020</t>
+          <t>13.11.2021</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4916,20 +4916,20 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sondre Aakerholm Adsen</t>
+          <t>Brage Gylseth Dahl</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1.27,78</t>
+          <t>1.26,19</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>30.09.2023</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4951,20 +4951,20 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Victor Voormolen Gutierrez</t>
+          <t>Philip Giske Nyman</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1.27,94</t>
+          <t>1.26,24</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>19.09.2020</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4986,20 +4986,20 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Eilert Juul Wolfgang</t>
+          <t>Emily Liv Liem</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1.27,94</t>
+          <t>1.38,08</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>08.02.2013</t>
+          <t>22.06.2019</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5021,25 +5021,25 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Brage Gylseth Dahl</t>
+          <t>Conrad Sippala Hassel</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1.28,40</t>
+          <t>1.27,23</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>02.11.2024</t>
+          <t>17.01.2020</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5056,20 +5056,20 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Philip Giske Nyman</t>
+          <t>Sondre Aakerholm Adsen</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1.29,45</t>
+          <t>1.27,78</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>30.09.2023</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5091,25 +5091,25 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Eirik Ingeberg Garshol</t>
+          <t>Victor Voormolen Gutierrez</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1.29,97</t>
+          <t>1.27,94</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>19.09.2020</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5126,20 +5126,20 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Christian Dahle-Øfsti</t>
+          <t>Eilert Juul Wolfgang</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1.30,31</t>
+          <t>1.27,94</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>05.10.2013</t>
+          <t>08.02.2013</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5161,25 +5161,25 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Isabel Ødegård Pedersen</t>
+          <t>Ingeborg Strandenes</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1.42,66</t>
+          <t>1.38,19</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5196,25 +5196,25 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Oscar Kvaløy Tiller</t>
+          <t>Sigurd Øie Seland</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1.30,89</t>
+          <t>1.29,79</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>20.11.2021</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5231,25 +5231,25 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Lin Carola Magdalene Nygren</t>
+          <t>Eirik Ingeberg Garshol</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1.43,38</t>
+          <t>1.29,97</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>15.03.2025</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5266,25 +5266,25 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Tamer Saleh Abuzid</t>
+          <t>Christian Dahle-Øfsti</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1.32,02</t>
+          <t>1.30,31</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>16.03.2019</t>
+          <t>05.10.2013</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5301,25 +5301,25 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Njål Høie</t>
+          <t>Fredrik Holberg</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1.34,03</t>
+          <t>1.30,14</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>07.02.2014</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5336,25 +5336,25 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Liv Løfaldli</t>
+          <t>Oscar Kvaløy Tiller</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1.49,01</t>
+          <t>1.30,89</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>20.11.2021</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5371,25 +5371,25 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Ingeborg Strandenes</t>
+          <t>Isabel Ødegård Pedersen</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1.50,16</t>
+          <t>1.42,66</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>14.03.2025</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5406,25 +5406,25 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Fredrik Holberg</t>
+          <t>Tamer Saleh Abuzid</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1.37,26</t>
+          <t>1.32,02</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>17.01.2025</t>
+          <t>16.03.2019</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5441,25 +5441,25 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>William Johannes Kirkelund Kristiansen</t>
+          <t>Liv Løfaldli</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>1.38,90</t>
+          <t>1.42,00</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>04.12.2022</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5481,20 +5481,20 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>1.52,41</t>
+          <t>1.43,41</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5511,25 +5511,25 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Liem Emily Liv</t>
+          <t>Njål Høie</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1.55,44</t>
+          <t>1.34,03</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>28.10.2018</t>
+          <t>07.02.2014</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5546,25 +5546,25 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Bernard Smuk</t>
+          <t>Olav Høyland Hofstad</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1.42,79</t>
+          <t>1.36,04</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5581,25 +5581,25 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Thomas Paulsen</t>
+          <t>William Johannes Kirkelund Kristiansen</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1.44,87</t>
+          <t>1.38,90</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>09.01.2015</t>
+          <t>04.12.2022</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5616,25 +5616,25 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Jakob M. Tjøstheim</t>
+          <t>Rasmus Larsen Natvig</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1.44,76</t>
+          <t>1.41,14</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>02.11.2013</t>
+          <t>01.11.2025</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5651,25 +5651,25 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Jesper Julius Sundseth Skjærli</t>
+          <t>Liem Emily Liv</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>1.45,35</t>
+          <t>1.55,44</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>28.10.2018</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5686,25 +5686,25 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>William Wale</t>
+          <t>Bernard Smuk</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1.45,33</t>
+          <t>1.42,79</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>07.02.2014</t>
+          <t>15.02.2025</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Kolvereid</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5721,20 +5721,20 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Sigurd Øie Seland</t>
+          <t>Jakob M. Tjøstheim</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>1.46,44</t>
+          <t>1.44,76</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>17.01.2025</t>
+          <t>02.11.2013</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5756,20 +5756,20 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Magnus Bakkejord</t>
+          <t>Thomas Paulsen</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1.47,83</t>
+          <t>1.44,87</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>29.10.2011</t>
+          <t>09.01.2015</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5791,25 +5791,25 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Ivan Erikovitch Alvestad</t>
+          <t>William Wale</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>1.48,22</t>
+          <t>1.45,33</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>09.11.2019</t>
+          <t>07.02.2014</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5826,25 +5826,25 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Ingvar Høgås Wik</t>
+          <t>Jesper Julius Sundseth Skjærli</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1.48,97</t>
+          <t>1.45,35</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>14.03.2015</t>
+          <t>10.05.2025</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5861,25 +5861,25 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Anton Hoel</t>
+          <t>Tymofii Dzisiak</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>1.49,50</t>
+          <t>1.45,53</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>18.01.2013</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5896,20 +5896,20 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Angelico Mikkel Andersen</t>
+          <t>Magnus Bakkejord</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>1.49,19</t>
+          <t>1.47,83</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>17.01.2020</t>
+          <t>29.10.2011</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -5931,25 +5931,25 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Olav Høyland Hofstad</t>
+          <t>Ivan Erikovitch Alvestad</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>1.49,17</t>
+          <t>1.48,22</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>09.11.2019</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5966,20 +5966,20 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Morten Johansen</t>
+          <t>Ingeborg Vold Kirkvold</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>1.50,34</t>
+          <t>1.59,78</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>15.01.2006</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -6001,25 +6001,25 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Brage Kaminka Heiberg</t>
+          <t>Ingvar Høgås Wik</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>1.51,43</t>
+          <t>1.48,97</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>12.11.2023</t>
+          <t>14.03.2015</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6036,25 +6036,25 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Tymofii Dzisiak</t>
+          <t>Anton Hoel</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>1.52,09</t>
+          <t>1.49,50</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>18.01.2013</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6071,20 +6071,20 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Setareh Kulsum Sigrid Feyzi</t>
+          <t>Angelico Mikkel Andersen</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2.06,57</t>
+          <t>1.49,19</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>20.05.2017</t>
+          <t>17.01.2020</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -6106,20 +6106,20 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Anniken Skjøstad</t>
+          <t>Morten Johansen</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2.06,91</t>
+          <t>1.50,34</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>17.01.2020</t>
+          <t>15.01.2006</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -6141,20 +6141,20 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Robin von Bargen</t>
+          <t>Brage Kaminka Heiberg</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>1.52,50</t>
+          <t>1.51,43</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>24.01.2009</t>
+          <t>12.11.2023</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -6176,25 +6176,25 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Sondre Thorgaard</t>
+          <t>Lilly Fludal Osland</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1.53,91</t>
+          <t>2.03,24</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>18.04.2021</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6211,25 +6211,25 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Cornelius Wik</t>
+          <t>Erik Solbakken Andersen</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>1.56,51</t>
+          <t>1.51,34</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>27.04.2024</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6246,20 +6246,20 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Rasmus Larsen Natvig</t>
+          <t>Anniken Skjøstad</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>1.57,20</t>
+          <t>2.06,91</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>27.04.2024</t>
+          <t>17.01.2020</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -6281,20 +6281,20 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Marit Søberg</t>
+          <t>Setareh Kulsum Sigrid Feyzi</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2.15,50</t>
+          <t>2.06,57</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>24.05.2008</t>
+          <t>20.05.2017</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -6316,25 +6316,25 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Sigurd Kristoffersen Torvik</t>
+          <t>Robin von Bargen</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2.02,93</t>
+          <t>1.52,50</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>24.01.2009</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6351,20 +6351,20 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Arild Håkonsen Stixrud</t>
+          <t>Mikkel Fenstad</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2.10,79</t>
+          <t>1.53,66</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>12.11.2023</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -6386,20 +6386,20 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Randi Leiknes</t>
+          <t>Sondre Thorgaard</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2.28,11</t>
+          <t>1.53,91</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>24.05.2008</t>
+          <t>18.04.2021</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -6421,25 +6421,25 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Magnus Hestvik Larsen</t>
+          <t>Cornelius Wik</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2.14,32</t>
+          <t>1.56,51</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>28.02.2009</t>
+          <t>27.04.2024</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6456,25 +6456,25 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Hans Otto Søyseth</t>
+          <t>Marit Søberg</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2.14,72</t>
+          <t>2.15,50</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>29.11.2014</t>
+          <t>24.05.2008</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6491,25 +6491,25 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Casper Dahle-Øfsti</t>
+          <t>Ragnhild Fjermestad</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2.16,37</t>
+          <t>2.14,81</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>02.11.2013</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6526,25 +6526,25 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Erik Solbakken Andersen</t>
+          <t>Sigurd Kristoffersen Torvik</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2.20,36</t>
+          <t>2.02,93</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>15.03.2024</t>
+          <t>10.05.2025</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6561,33 +6561,208 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
+          <t>Arild Håkonsen Stixrud</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2.10,79</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>48</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>12.11.2023</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Randi Leiknes</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2.28,11</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>48</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>24.05.2008</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Magnus Hestvik Larsen</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2.14,32</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>45</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>28.02.2009</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Stjørdal</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Hans Otto Søyseth</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2.14,72</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>44</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>29.11.2014</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Stjørdal</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Casper Dahle-Øfsti</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2.16,37</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>43</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>02.11.2013</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
           <t>Eirik Solligård</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B181" t="inlineStr">
         <is>
           <t>2.23,65</t>
         </is>
       </c>
-      <c r="C176" t="n">
+      <c r="C181" t="n">
         <v>36</v>
       </c>
-      <c r="D176" t="inlineStr">
+      <c r="D181" t="inlineStr">
         <is>
           <t>24.05.2008</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Trondheim</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -8467,12 +8642,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Jo Kebriel Stølhaug Nor</t>
+          <t>Bjørn Eimar Endal Sorteberg</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.14,79</t>
+          <t>1.14,74</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -8480,12 +8655,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>13.04.2024</t>
+          <t>28.06.2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -8502,12 +8677,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Bjørn Eimar Endal Sorteberg</t>
+          <t>Jo Kebriel Stølhaug Nor</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1.14,74</t>
+          <t>1.14,79</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -8515,12 +8690,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>28.06.2025</t>
+          <t>13.04.2024</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -8607,12 +8782,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Erlend Søderlund</t>
+          <t>Vårin Berge Jensås</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1.17,11</t>
+          <t>1.26,55</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -8620,12 +8795,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>04.07.2013</t>
+          <t>15.04.2018</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -8642,12 +8817,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Vårin Berge Jensås</t>
+          <t>Erlend Søderlund</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1.26,55</t>
+          <t>1.17,11</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -8655,12 +8830,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>15.04.2018</t>
+          <t>04.07.2013</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -9840,7 +10015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G161"/>
+  <dimension ref="A1:G165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10159,7 +10334,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Amanda Husan Ehrnholm</t>
+          <t>Sanna Josefin Husan Ehrnholm</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -10172,12 +10347,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16.01.2016</t>
+          <t>03.12.2016</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -10194,7 +10369,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sanna Josefin Husan Ehrnholm</t>
+          <t>Amanda Husan Ehrnholm</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -10207,12 +10382,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>03.12.2016</t>
+          <t>16.01.2016</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -10474,12 +10649,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rebekka Wangberg</t>
+          <t>Sara Juul Wolfgang</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.10,13</t>
+          <t>1.10,15</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -10487,12 +10662,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>28.10.2018</t>
+          <t>01.12.2013</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -10509,12 +10684,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sara Juul Wolfgang</t>
+          <t>Rebekka Wangberg</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.10,15</t>
+          <t>1.10,13</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -10522,12 +10697,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>01.12.2013</t>
+          <t>28.10.2018</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -11174,25 +11349,25 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Miriam Vedvik</t>
+          <t>Sissel Furuholt Valle</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.14,97</t>
+          <t>1.12,98</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>17.10.2008</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lambertseter</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -11209,25 +11384,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kristina Elena Bjørklund Mora</t>
+          <t>Miriam Vedvik</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.15,52</t>
+          <t>1.14,97</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>09.02.2013</t>
+          <t>17.10.2008</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Lambertseter</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -11244,20 +11419,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cesilie Solberg Jørgensen</t>
+          <t>Kristina Elena Bjørklund Mora</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.15,76</t>
+          <t>1.15,52</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>02.11.2013</t>
+          <t>09.02.2013</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -11279,20 +11454,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kirsti Bjørnsdatter Paulsen</t>
+          <t>Cesilie Solberg Jørgensen</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.15,86</t>
+          <t>1.15,76</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10.02.2018</t>
+          <t>02.11.2013</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -11314,25 +11489,25 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Torborg Duesten Blokkum</t>
+          <t>Kirsti Bjørnsdatter Paulsen</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.16,24</t>
+          <t>1.15,86</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>02.04.2011</t>
+          <t>10.02.2018</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -11384,25 +11559,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Olea Winnberg</t>
+          <t>Torborg Duesten Blokkum</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.16,83</t>
+          <t>1.16,24</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>02.04.2011</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -11419,25 +11594,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Maja Graczyk</t>
+          <t>Ada Fludal Osland</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.16,89</t>
+          <t>1.14,56</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>22.06.2019</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -11454,25 +11629,25 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tage Singstad</t>
+          <t>Olea Winnberg</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.08,11</t>
+          <t>1.16,83</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10.04.2011</t>
+          <t>15.02.2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Kolvereid</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -11489,25 +11664,25 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Camilla Dahle-Øfsti</t>
+          <t>Maja Graczyk</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.17,09</t>
+          <t>1.16,89</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>07.02.2015</t>
+          <t>22.06.2019</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -11524,25 +11699,25 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Vilde Austmo</t>
+          <t>Tage Singstad</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.17,12</t>
+          <t>1.08,11</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10.02.2018</t>
+          <t>10.04.2011</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -11559,25 +11734,25 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sissel Furuholt Valle</t>
+          <t>Vilde Austmo</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.17,22</t>
+          <t>1.17,12</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>08.06.2025</t>
+          <t>10.02.2018</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Porsgrunn</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -11594,20 +11769,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Heidi Elisabeth Ysland</t>
+          <t>Camilla Dahle-Øfsti</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.17,34</t>
+          <t>1.17,09</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>11.02.2017</t>
+          <t>07.02.2015</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -11629,25 +11804,25 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Diana Stafsnes Califano</t>
+          <t>Heidi Elisabeth Ysland</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.17,54</t>
+          <t>1.17,34</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>17.01.2020</t>
+          <t>11.02.2017</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -11664,25 +11839,25 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Embla Mimi Baarholm</t>
+          <t>Diana Stafsnes Califano</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.17,71</t>
+          <t>1.17,54</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>16.03.2019</t>
+          <t>17.01.2020</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -11699,25 +11874,25 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Solveig Natvig Løvseth</t>
+          <t>Embla Mimi Baarholm</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.17,76</t>
+          <t>1.17,71</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>08.02.2014</t>
+          <t>16.03.2019</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -11734,12 +11909,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Live Killingberg Sandberg</t>
+          <t>Solveig Natvig Løvseth</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1.17,78</t>
+          <t>1.17,76</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -11747,7 +11922,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>24.10.2020</t>
+          <t>08.02.2014</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -11769,25 +11944,25 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Irja Gravdahl</t>
+          <t>Live Killingberg Sandberg</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1.18,43</t>
+          <t>1.17,78</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>20.11.2010</t>
+          <t>24.10.2020</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11804,25 +11979,25 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ingrid Elverum</t>
+          <t>Irja Gravdahl</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1.19,01</t>
+          <t>1.18,43</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>08.02.2014</t>
+          <t>20.11.2010</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11874,25 +12049,25 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Oda Sem Austmo</t>
+          <t>Ingrid Elverum</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1.19,82</t>
+          <t>1.19,01</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>05.10.2013</t>
+          <t>08.02.2014</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11909,20 +12084,20 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Inga Maren Steinsdotter Nestgaard</t>
+          <t>Oda Sem Austmo</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1.19,93</t>
+          <t>1.19,82</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>16.06.2018</t>
+          <t>05.10.2013</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -11944,20 +12119,20 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Malin Schanke Tømmervik</t>
+          <t>Inga Maren Steinsdotter Nestgaard</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1.20,07</t>
+          <t>1.19,93</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>19.06.2010</t>
+          <t>16.06.2018</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -11979,20 +12154,20 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Helene Rapp Karlsen</t>
+          <t>Malin Schanke Tømmervik</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1.20,13</t>
+          <t>1.20,07</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>17.01.2020</t>
+          <t>19.06.2010</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -12014,12 +12189,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Helle Krogstad</t>
+          <t>Helene Rapp Karlsen</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1.20,20</t>
+          <t>1.20,13</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -12027,12 +12202,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>09.02.2008</t>
+          <t>17.01.2020</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12049,25 +12224,25 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Dorottya Csejtey</t>
+          <t>Helle Krogstad</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1.20,50</t>
+          <t>1.20,20</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>16.06.2018</t>
+          <t>09.02.2008</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12084,25 +12259,25 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Lisa Ling Klauseth Liasjø</t>
+          <t>Dorottya Csejtey</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1.20,58</t>
+          <t>1.20,50</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>19.10.2019</t>
+          <t>16.06.2018</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12119,12 +12294,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Erle Kullerud Ytrehus</t>
+          <t>Lisa Ling Klauseth Liasjø</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1.20,62</t>
+          <t>1.20,58</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -12132,12 +12307,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>19.10.2019</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12154,25 +12329,25 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Marthe Kalvik</t>
+          <t>Erle Kullerud Ytrehus</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1.20,70</t>
+          <t>1.20,62</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>25.01.2008</t>
+          <t>15.03.2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12189,25 +12364,25 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ada Fludal Osland</t>
+          <t>Marthe Kalvik</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1.20,88</t>
+          <t>1.20,70</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>25.01.2008</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -12364,12 +12539,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Annika Krill</t>
+          <t>Marcelina Puzio</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1.21,64</t>
+          <t>1.19,56</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -12377,7 +12552,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>04.02.2005</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -12399,20 +12574,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ane Viken Refseth</t>
+          <t>Annika Krill</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1.22,22</t>
+          <t>1.21,64</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>31.10.2015</t>
+          <t>04.02.2005</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -12434,25 +12609,25 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Emre Vold Kirkvold</t>
+          <t>Ane Viken Refseth</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1.12,76</t>
+          <t>1.22,22</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>31.10.2015</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -12469,12 +12644,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Kyrre Moljord</t>
+          <t>Emre Vold Kirkvold</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1.12,72</t>
+          <t>1.12,76</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -12482,12 +12657,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>04.02.2005</t>
+          <t>15.03.2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -12504,20 +12679,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Linn Amalie Aresvik</t>
+          <t>Kyrre Moljord</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1.22,68</t>
+          <t>1.12,72</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>03.11.2012</t>
+          <t>04.02.2005</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -12539,20 +12714,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Hedda Østgaard</t>
+          <t>Linn Amalie Aresvik</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1.22,77</t>
+          <t>1.22,68</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>22.01.2010</t>
+          <t>03.11.2012</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -12574,25 +12749,25 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Julie Hegvik</t>
+          <t>Alexandra Contreras Jimenez</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1.22,95</t>
+          <t>1.20,74</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>19.10.2007</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Lambertseter</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -12609,20 +12784,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Ada Viken Refseth</t>
+          <t>Hedda Østgaard</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1.23,07</t>
+          <t>1.22,77</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>17.01.2020</t>
+          <t>22.01.2010</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -12644,25 +12819,25 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Marcelina Puzio</t>
+          <t>Julie Hegvik</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1.23,60</t>
+          <t>1.22,95</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>29.03.2025</t>
+          <t>19.10.2007</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Lambertseter</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -12679,25 +12854,25 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Emma Lu Tjeldvoll</t>
+          <t>Ada Viken Refseth</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1.23,65</t>
+          <t>1.23,07</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>22.10.2022</t>
+          <t>17.01.2020</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -12714,25 +12889,25 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Othelie Annette Høie</t>
+          <t>Emma Lu Tjeldvoll</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1.23,80</t>
+          <t>1.23,65</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>17.01.2015</t>
+          <t>22.10.2022</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -12749,20 +12924,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Olivia Sterud Prytz</t>
+          <t>Othelie Annette Høie</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1.24,34</t>
+          <t>1.23,80</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>16.11.2019</t>
+          <t>17.01.2015</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -12784,25 +12959,25 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Erika Nicole Hagen</t>
+          <t>Olivia Sterud Prytz</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1.24,37</t>
+          <t>1.24,34</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>19.03.2022</t>
+          <t>16.11.2019</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Orkanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -12819,25 +12994,25 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Susanne Kolloen</t>
+          <t>Erika Nicole Hagen</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1.24,79</t>
+          <t>1.24,37</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>04.09.2021</t>
+          <t>19.03.2022</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Orkanger</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -12854,25 +13029,25 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Thea Lervold Høffler</t>
+          <t>Susanne Kolloen</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1.24,96</t>
+          <t>1.24,79</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>06.02.2016</t>
+          <t>04.09.2021</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -12889,20 +13064,20 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Mari Helen Hammer</t>
+          <t>Sofie Hoff</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1.25,05</t>
+          <t>1.22,82</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>04.02.2005</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -12924,25 +13099,25 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Hanne Søyseth</t>
+          <t>Thea Lervold Høffler</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1.25,12</t>
+          <t>1.24,96</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>16.01.2016</t>
+          <t>06.02.2016</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -12959,25 +13134,25 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Hedda Grimstad-Johannessen</t>
+          <t>Mari Helen Hammer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1.25,22</t>
+          <t>1.25,05</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>04.09.2021</t>
+          <t>04.02.2005</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -12994,20 +13169,20 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Julie Wiik Arnesen</t>
+          <t>Hanne Søyseth</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1.26,11</t>
+          <t>1.25,12</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>19.09.2020</t>
+          <t>16.01.2016</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -13029,25 +13204,25 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Ola vatn Gundersen</t>
+          <t>Hedda Grimstad-Johannessen</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1.16,18</t>
+          <t>1.25,22</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>29.09.2019</t>
+          <t>04.09.2021</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -13064,25 +13239,25 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Isabella Johanne Debik</t>
+          <t>Julie Wiik Arnesen</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1.26,32</t>
+          <t>1.26,11</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>19.09.2020</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -13099,25 +13274,25 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Marthe Eline Waagø-Hansen</t>
+          <t>Ola vatn Gundersen</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1.26,41</t>
+          <t>1.16,18</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>07.10.2006</t>
+          <t>29.09.2019</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -13134,25 +13309,25 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Emilie Ying Ulstad Hovland</t>
+          <t>Isabella Johanne Debik</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1.26,66</t>
+          <t>1.26,32</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>28.03.2025</t>
+          <t>10.05.2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -13169,25 +13344,25 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Thora Bjarnøe Brandsegg</t>
+          <t>Marthe Eline Waagø-Hansen</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1.26,63</t>
+          <t>1.26,41</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>19.03.2022</t>
+          <t>07.10.2006</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Orkanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -13204,25 +13379,25 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Aurora Alexandra Bjordal</t>
+          <t>Thora Bjarnøe Brandsegg</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1.28,05</t>
+          <t>1.26,63</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>23.10.2021</t>
+          <t>19.03.2022</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Orkanger</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -13239,25 +13414,25 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Kine Marie Sørensen</t>
+          <t>Emilie Ying Ulstad Hovland</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1.28,12</t>
+          <t>1.26,66</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>17.04.2005</t>
+          <t>28.03.2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -13274,25 +13449,25 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Oline Skjønberg</t>
+          <t>Helle Johnsen Selsås</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1.28,56</t>
+          <t>1.25,08</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>17.01.2020</t>
+          <t>01.11.2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -13309,25 +13484,25 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Alisa Kulagina</t>
+          <t>Aurora Alexandra Bjordal</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1.29,23</t>
+          <t>1.28,05</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>23.10.2021</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -13344,25 +13519,25 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Frida Pauline Busch</t>
+          <t>Kine Marie Sørensen</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1.29,27</t>
+          <t>1.28,12</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>13.02.2022</t>
+          <t>17.04.2005</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -13379,25 +13554,25 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Guro Rønningen Osmoen</t>
+          <t>Oline Skjønberg</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1.29,43</t>
+          <t>1.28,56</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>17.01.2020</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -13414,25 +13589,25 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Izabele Farias Ribeiro</t>
+          <t>Alisa Kulagina</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1.29,72</t>
+          <t>1.26,34</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>07.02.2015</t>
+          <t>01.11.2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -13449,25 +13624,25 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Hansine Rindberg Monsø</t>
+          <t>Frida Pauline Busch</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1.29,92</t>
+          <t>1.29,27</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>15.03.2024</t>
+          <t>13.02.2022</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -13484,25 +13659,25 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Helle Johnsen Selsås</t>
+          <t>Guro Rønningen Osmoen</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1.30,43</t>
+          <t>1.29,43</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>15.03.2025</t>
+          <t>15.02.2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Kolvereid</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -13519,25 +13694,25 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Maria Bøe</t>
+          <t>Sofie Hepsø</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1.30,37</t>
+          <t>1.27,21</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>14.02.2010</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -13554,20 +13729,20 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Silje Dahle</t>
+          <t>Kristina Aleman Sandsund</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1.30,55</t>
+          <t>1.27,40</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>28.10.2018</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -13589,25 +13764,25 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Anna Svendsen</t>
+          <t>Izabele Farias Ribeiro</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1.30,68</t>
+          <t>1.29,72</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>16.03.2019</t>
+          <t>07.02.2015</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -13624,25 +13799,25 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sofie Hoff</t>
+          <t>Hansine Rindberg Monsø</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1.32,04</t>
+          <t>1.29,92</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>17.01.2025</t>
+          <t>15.03.2024</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -13659,25 +13834,25 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Anahita Koushan</t>
+          <t>Maria Bøe</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1.32,72</t>
+          <t>1.30,37</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>16.11.2019</t>
+          <t>14.02.2010</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -13694,20 +13869,20 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Elisaveta Røste</t>
+          <t>Silje Dahle</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1.32,86</t>
+          <t>1.30,55</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>17.01.2020</t>
+          <t>28.10.2018</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -13729,25 +13904,25 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Ingrid Johansen</t>
+          <t>Anna Svendsen</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1.33,16</t>
+          <t>1.30,68</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>13.01.2007</t>
+          <t>16.03.2019</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -13764,25 +13939,25 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Aase Bjørnsdatter Paulsen</t>
+          <t>Nicole Kulagina</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1.33,13</t>
+          <t>1.28,67</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>06.02.2016</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -13799,20 +13974,20 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Magne Petersen</t>
+          <t>Anahita Koushan</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1.22,51</t>
+          <t>1.32,72</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>09.02.2013</t>
+          <t>16.11.2019</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -13834,20 +14009,20 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Anita Klungervik</t>
+          <t>Elisaveta Røste</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1.33,53</t>
+          <t>1.32,86</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>26.01.2024</t>
+          <t>17.01.2020</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -13869,20 +14044,20 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Selma Strandjord Lillerødvann</t>
+          <t>Aase Bjørnsdatter Paulsen</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1.35,22</t>
+          <t>1.33,13</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>16.03.2024</t>
+          <t>06.02.2016</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -13904,20 +14079,20 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Pia Helena Wildhagen</t>
+          <t>Ingrid Johansen</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1.35,37</t>
+          <t>1.33,16</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>16.06.2018</t>
+          <t>13.01.2007</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -13939,20 +14114,20 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Helene Marie Haram</t>
+          <t>Magne Petersen</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1.36,35</t>
+          <t>1.22,51</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>17.01.2020</t>
+          <t>09.02.2013</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -13974,20 +14149,20 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Chloe Branlat</t>
+          <t>Anita Klungervik</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1.36,95</t>
+          <t>1.33,53</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>17.01.2025</t>
+          <t>26.01.2024</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -14009,25 +14184,25 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Hilde Stene Rygh</t>
+          <t>Michaela Josefin Abeleva Barrera</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1.37,08</t>
+          <t>1.31,74</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>03.03.2018</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -14044,25 +14219,25 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Alexandra Contreras Jimenez</t>
+          <t>Elina Arefjord Spangelo</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1.37,37</t>
+          <t>1.32,23</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>03.12.2023</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -14079,25 +14254,25 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Michaela Josefin Abeleva Barrera</t>
+          <t>Selma Strandjord Lillerødvann</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1.37,44</t>
+          <t>1.35,22</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>16.03.2024</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -14114,20 +14289,20 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Elise Øystrøm Tyvold</t>
+          <t>Pia Helena Wildhagen</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1.37,40</t>
+          <t>1.35,37</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>16.11.2019</t>
+          <t>16.06.2018</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -14149,25 +14324,25 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Sara Skaalvik Trelstad</t>
+          <t>Helene Marie Haram</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1.37,62</t>
+          <t>1.36,35</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>07.02.2014</t>
+          <t>17.01.2020</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -14184,20 +14359,20 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Synnøve Fevang</t>
+          <t>Chloe Branlat</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1.38,10</t>
+          <t>1.36,95</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>20.05.2006</t>
+          <t>17.01.2025</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -14219,25 +14394,25 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Amalie Solvoll</t>
+          <t>Hilde Stene Rygh</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1.38,18</t>
+          <t>1.37,08</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>18.01.2019</t>
+          <t>03.03.2018</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -14254,25 +14429,25 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Nicole Kulagina</t>
+          <t>Elise Øystrøm Tyvold</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1.38,87</t>
+          <t>1.37,40</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>16.11.2019</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -14289,25 +14464,25 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Elina Arefjord Spangelo</t>
+          <t>Sara Skaalvik Trelstad</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1.39,31</t>
+          <t>1.37,62</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>07.02.2014</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -14324,25 +14499,25 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Helle Lundgren</t>
+          <t>Synnøve Fevang</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1.39,30</t>
+          <t>1.38,10</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>11.02.2023</t>
+          <t>20.05.2006</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -14359,25 +14534,25 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sofie Hepsø</t>
+          <t>Amalie Solvoll</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1.39,66</t>
+          <t>1.38,18</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>15.03.2024</t>
+          <t>18.01.2019</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -14394,25 +14569,25 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Line Steine Bertelsen</t>
+          <t>Ina Birgitte Eidsmo Hova</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1.40,02</t>
+          <t>1.36,27</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>20.11.2021</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -14429,25 +14604,25 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Elsa Dragsten Wake</t>
+          <t>Helle Lundgren</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1.40,49</t>
+          <t>1.39,30</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>11.02.2023</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -14464,25 +14639,25 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sofia Bjørklund Mora</t>
+          <t>Line Steine Bertelsen</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1.41,13</t>
+          <t>1.40,02</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>29.11.2014</t>
+          <t>20.11.2021</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -14499,25 +14674,25 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Ida Fiskaa Barstad</t>
+          <t>Elsa Dragsten Wake</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1.43,03</t>
+          <t>1.40,49</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>17.01.2020</t>
+          <t>10.05.2025</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -14534,25 +14709,25 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Marte Hemmer</t>
+          <t>Sofia Bjørklund Mora</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1.43,90</t>
+          <t>1.41,13</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>14.01.2005</t>
+          <t>29.11.2014</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -14569,25 +14744,25 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Ina Birgitte Eidsmo Hova</t>
+          <t>Ida Fiskaa Barstad</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1.44,61</t>
+          <t>1.43,03</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>02.11.2024</t>
+          <t>17.01.2020</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -14604,25 +14779,25 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Amalie Gylseth Dahl</t>
+          <t>Marte Hemmer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1.45,39</t>
+          <t>1.43,90</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>03.12.2023</t>
+          <t>14.01.2005</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -14674,25 +14849,25 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Madeleine Tran Wæraas</t>
+          <t>Amalie Gylseth Dahl</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1.45,66</t>
+          <t>1.45,39</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>26.10.2019</t>
+          <t>03.12.2023</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -14709,25 +14884,25 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Ingrid Skye Naustvoll</t>
+          <t>Madeleine Tran Wæraas</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1.46,39</t>
+          <t>1.45,66</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>23.11.2013</t>
+          <t>26.10.2019</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -14744,20 +14919,20 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Aurora Dahl Bere</t>
+          <t>Ingrid Skye Naustvoll</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1.46,55</t>
+          <t>1.46,39</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>22.02.2025</t>
+          <t>23.11.2013</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -14779,25 +14954,25 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sigrid Moen Henriksen</t>
+          <t>Aurora Dahl Bere</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1.46,92</t>
+          <t>1.46,55</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>18.03.2023</t>
+          <t>22.02.2025</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -14814,20 +14989,20 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Mia Bretun Finserå</t>
+          <t>Sigrid Moen Henriksen</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1.48,12</t>
+          <t>1.46,92</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>03.11.2012</t>
+          <t>18.03.2023</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -14849,20 +15024,20 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Cathrine Hegle</t>
+          <t>Mia Bretun Finserå</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>1.52,85</t>
+          <t>1.48,12</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>13.02.2011</t>
+          <t>03.11.2012</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -14884,25 +15059,25 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Marie Wærnes Blom</t>
+          <t>Hedda Gätzschmann</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>1.54,25</t>
+          <t>1.49,40</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -14919,25 +15094,25 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Emilie Sandvik Gangåssæter</t>
+          <t>Cathrine Hegle</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1.54,88</t>
+          <t>1.52,85</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>28.09.2019</t>
+          <t>13.02.2011</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -14954,25 +15129,25 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Arne Martin Einarsrud Rismoen</t>
+          <t>Marie Wærnes Blom</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1.41,70</t>
+          <t>1.54,25</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>19.09.2020</t>
+          <t>14.03.2025</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -14989,20 +15164,20 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Luma Nicole Farias Kristiansen</t>
+          <t>Louise Thys</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1.56,41</t>
+          <t>1.51,91</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>16.11.2019</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -15024,25 +15199,25 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Nicoline Vinje</t>
+          <t>Emilie Sandvik Gangåssæter</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1.58,19</t>
+          <t>1.54,88</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>28.09.2019</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -15059,25 +15234,25 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Camila Dorao</t>
+          <t>Arne Martin Einarsrud Rismoen</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>1.59,63</t>
+          <t>1.41,70</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>02.11.2024</t>
+          <t>19.09.2020</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -15094,25 +15269,25 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Louise Thys</t>
+          <t>Luma Nicole Farias Kristiansen</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1.59,76</t>
+          <t>1.56,41</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>14.03.2025</t>
+          <t>16.11.2019</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -15129,25 +15304,25 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Ella Katrine Lind Bøckman</t>
+          <t>Nicoline Vinje</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2.00,63</t>
+          <t>1.58,19</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>17.01.2020</t>
+          <t>10.05.2025</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -15164,25 +15339,25 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Aida Smalø Moen</t>
+          <t>Camila Dorao</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2.02,91</t>
+          <t>1.59,63</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>03.12.2011</t>
+          <t>02.11.2024</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -15199,25 +15374,25 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Ilaria Kari Cherubini</t>
+          <t>Ella Katrine Lind Bøckman</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2.03,19</t>
+          <t>2.00,63</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>17.01.2020</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -15234,25 +15409,25 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Oda Emilie Krogh</t>
+          <t>Aida Smalø Moen</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2.07,49</t>
+          <t>2.02,91</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>13.11.2021</t>
+          <t>03.12.2011</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -15269,25 +15444,25 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Charlotte Talseth</t>
+          <t>Ilaria Kari Cherubini</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2.08,27</t>
+          <t>2.03,19</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>22.02.2025</t>
+          <t>10.05.2025</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -15304,20 +15479,20 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Frida Merethe Norli Eidsvåg</t>
+          <t>Sigrid Gylseth Dahl</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2.08,56</t>
+          <t>2.00,68</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>01.11.2014</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -15339,20 +15514,20 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Sigrid Gylseth Dahl</t>
+          <t>Oda Emilie Krogh</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2.08,76</t>
+          <t>2.07,49</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>13.11.2021</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -15374,25 +15549,25 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Ramona Vutudal</t>
+          <t>Live Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2.18,26</t>
+          <t>2.04,87</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>18.04.2009</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -15409,25 +15584,25 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Sara Olea  Riseth Moe</t>
+          <t>Frida Merethe Norli Eidsvåg</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2.23,77</t>
+          <t>2.08,56</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>01.11.2014</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -15444,33 +15619,173 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
+          <t>Charlotte Talseth</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2.08,27</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>74</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>22.02.2025</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Stjørdal</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Oda Brennhaug Tangen</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2.09,59</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>67</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>08.11.2025</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Ramona Vutudal</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2.18,26</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>59</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>18.04.2009</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Kristiansund</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Sara Olea  Riseth Moe</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2.23,77</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>53</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>10.05.2025</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Verdal</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
           <t>Camilla Gervasoni</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
+      <c r="B165" t="inlineStr">
         <is>
           <t>2.25,16</t>
         </is>
       </c>
-      <c r="C161" t="n">
+      <c r="C165" t="n">
         <v>51</v>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="D165" t="inlineStr">
         <is>
           <t>03.12.2011</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
+      <c r="E165" t="inlineStr">
         <is>
           <t>Stjørdal</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
@@ -16720,12 +17035,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kirsti Bjørnsdatter Paulsen</t>
+          <t>Sigrid Eldholm</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.18,99</t>
+          <t>1.19,00</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -16733,12 +17048,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>09.06.2018</t>
+          <t>02.07.2022</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -16755,12 +17070,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sigrid Eldholm</t>
+          <t>Kirsti Bjørnsdatter Paulsen</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.19,00</t>
+          <t>1.18,99</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -16768,12 +17083,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>02.07.2022</t>
+          <t>09.06.2018</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -16790,12 +17105,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Inga Maren Steinsdotter Nestgaard</t>
+          <t>Stine Tveit</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.19,16</t>
+          <t>1.19,18</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -16803,12 +17118,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>02.07.2016</t>
+          <t>25.04.2009</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -16825,12 +17140,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Stine Tveit</t>
+          <t>Inga Maren Steinsdotter Nestgaard</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.19,18</t>
+          <t>1.19,16</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -16838,12 +17153,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>25.04.2009</t>
+          <t>02.07.2016</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -17700,12 +18015,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ingrid Elverum</t>
+          <t>Magne Petersen</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1.29,88</t>
+          <t>1.20,03</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -17713,12 +18028,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>13.04.2013</t>
+          <t>04.07.2013</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -17735,12 +18050,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Magne Petersen</t>
+          <t>Elise Nygård</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1.20,03</t>
+          <t>1.29,88</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -17748,12 +18063,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>04.07.2013</t>
+          <t>24.04.2010</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -17770,7 +18085,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Elise Nygård</t>
+          <t>Ingrid Elverum</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -17783,12 +18098,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>24.04.2010</t>
+          <t>13.04.2013</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
